--- a/erp-server/erp-server-wms/src/main/resources/excel/sampleScrapInfoTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/sampleScrapInfoTemplate.xlsx
@@ -1,15 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="22560" windowHeight="11120"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,9 +27,107 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>序号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>报废日期</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>报废人</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>报废部门</t>
+    </r>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -47,6 +143,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -57,7 +160,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>质检通知数量</t>
+      <t>报废数量</t>
     </r>
   </si>
 </sst>
@@ -533,7 +636,9 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -680,8 +785,12 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -734,7 +843,221 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -744,9 +1067,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="WPS">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -754,39 +1077,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4874CB"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="EE822F"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="F2BA02"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="75BD42"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="30C0B4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="E54C5E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0026E5"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="7E1FAD"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="WPS">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -856,169 +1179,132 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="WPS">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumOff val="17500"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:hueOff val="-2520000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:gradFill>
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="phClr">
+                  <a:hueOff val="-4200000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="phClr"/>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="2700000" scaled="1"/>
+          </a:gradFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
+            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:schemeClr val="phClr">
+                <a:alpha val="60000"/>
+              </a:schemeClr>
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
+            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1030,52 +1316,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="17.375" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="1" max="1" width="19.7272727272727" customWidth="1"/>
+    <col min="2" max="2" width="20.0909090909091" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="17.7272727272727" customWidth="1"/>
+    <col min="6" max="6" width="15.5454545454545" customWidth="1"/>
+    <col min="7" max="7" width="17.8181818181818" customWidth="1"/>
+    <col min="8" max="8" width="19.7272727272727" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:2">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
-      <formula1>1</formula1>
-      <formula2>10000000</formula2>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/erp-server/erp-server-wms/src/main/resources/excel/sampleScrapInfoTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/sampleScrapInfoTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22560" windowHeight="11120"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <r>
       <rPr>
@@ -155,6 +155,27 @@
     <r>
       <rPr>
         <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>使用方</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -162,6 +183,9 @@
       </rPr>
       <t>报废数量</t>
     </r>
+  </si>
+  <si>
+    <t>明细备注</t>
   </si>
 </sst>
 </file>
@@ -174,7 +198,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -331,6 +355,12 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1316,20 +1346,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="7"/>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="19.7272727272727" customWidth="1"/>
-    <col min="2" max="2" width="20.0909090909091" customWidth="1"/>
+    <col min="1" max="1" width="19.725" customWidth="1"/>
+    <col min="2" max="2" width="20.0916666666667" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="17.7272727272727" customWidth="1"/>
-    <col min="6" max="6" width="15.5454545454545" customWidth="1"/>
-    <col min="7" max="7" width="17.8181818181818" customWidth="1"/>
-    <col min="8" max="8" width="19.7272727272727" customWidth="1"/>
+    <col min="5" max="5" width="17.725" customWidth="1"/>
+    <col min="6" max="7" width="15.5416666666667" customWidth="1"/>
+    <col min="8" max="8" width="17.8166666666667" customWidth="1"/>
+    <col min="9" max="9" width="19.725" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1351,8 +1381,11 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>4</v>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/sampleScrapInfoTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/sampleScrapInfoTemplate.xlsx
@@ -814,11 +814,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1349,42 +1352,42 @@
   <dimension ref="A1:I1"/>
   <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="19.725" customWidth="1"/>
-    <col min="2" max="2" width="20.0916666666667" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="17.725" customWidth="1"/>
-    <col min="6" max="7" width="15.5416666666667" customWidth="1"/>
-    <col min="8" max="8" width="17.8166666666667" customWidth="1"/>
-    <col min="9" max="9" width="19.725" customWidth="1"/>
+    <col min="1" max="1" width="19.725" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.0916666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.725" style="1" customWidth="1"/>
+    <col min="6" max="7" width="15.5416666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.8166666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.725" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
